--- a/excel/Nordstreet.xlsx
+++ b/excel/Nordstreet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Nordstreet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FD33E1-E445-49AB-90B3-D85C35CE0346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C49BCC-641F-40CF-8CCC-CC4EBED43235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="1" r:id="rId1"/>
@@ -430,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +440,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -620,6 +626,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3325,39 +3334,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="O1" s="37" t="s">
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="O1" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="38" t="s">
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="T1" s="39"/>
-      <c r="U1" s="38" t="s">
+      <c r="T1" s="40"/>
+      <c r="U1" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="39"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:29" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -3491,7 +3500,7 @@
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
-        <v>1033.8800000000001</v>
+        <v>1023.29</v>
       </c>
       <c r="Q3" s="5">
         <f>Pinigai!H2</f>
@@ -3499,31 +3508,31 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>77.970000000000027</v>
+        <v>91.860000000000127</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
-        <v>422.12</v>
+        <v>432.71</v>
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>112.91</v>
+        <v>116.21</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1111.8500000000001</v>
+        <v>1115.1500000000001</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>161.85000000000014</v>
+        <v>165.15000000000009</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>0.17036842105263172</v>
+        <v>0.17384210526315799</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15313978791236879</v>
+        <v>0.15337591767311098</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mesiheina tee 5 ir 8 (1)'!AA2</f>
@@ -3568,11 +3577,11 @@
       </c>
       <c r="J4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!B13</f>
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!S3</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L4" s="5">
         <f>'Bistryčios g. 27 (3)'!N3</f>
@@ -3625,11 +3634,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!B13</f>
-        <v>-204</v>
+        <v>-211</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!S3</f>
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="L5" s="5">
         <f>'2 MW saulės elektrinių par. (9)'!N3</f>
@@ -3682,7 +3691,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!B13</f>
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!S3</f>
@@ -3967,11 +3976,11 @@
       </c>
       <c r="J11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!B13</f>
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!S3</f>
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!N3</f>
@@ -4081,11 +4090,11 @@
       </c>
       <c r="J13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!B13</f>
-        <v>-25</v>
+        <v>-32</v>
       </c>
       <c r="K13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!S3</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L13" s="5">
         <f>'Vilniaus g. 38 38A 38B (1)'!N3</f>
@@ -4195,7 +4204,7 @@
       </c>
       <c r="J15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!B13</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K15" s="9" t="str">
         <f ca="1">'Viensėdžio g. 36A (3)'!S3</f>
@@ -4207,7 +4216,7 @@
       </c>
       <c r="M15" s="5">
         <f>'Viensėdžio g. 36A (3)'!P3</f>
-        <v>5.07</v>
+        <v>5.59</v>
       </c>
       <c r="AC15" s="5" t="str">
         <f ca="1">'Viensėdžio g. 36A (3)'!AA2</f>
@@ -4252,7 +4261,7 @@
       </c>
       <c r="J16" s="9">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!B13</f>
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="K16" s="9" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!S3</f>
@@ -4264,7 +4273,7 @@
       </c>
       <c r="M16" s="5">
         <f>'Šaltinio g. 7, Panevėžys (1)'!P3</f>
-        <v>5.36</v>
+        <v>5.91</v>
       </c>
       <c r="AC16" s="5" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!AA2</f>
@@ -4309,11 +4318,11 @@
       </c>
       <c r="J17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!B13</f>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!S3</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L17" s="5">
         <f>'Mozūriškių g. 17 - 3, Vilnius'!N3</f>
@@ -4366,11 +4375,11 @@
       </c>
       <c r="J18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!B13</f>
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!S3</f>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L18" s="5">
         <f>'Parko g. 21 Pergalės g. 36A (1)'!N3</f>
@@ -4480,7 +4489,7 @@
       </c>
       <c r="J20" s="9">
         <f ca="1">'Baltų Avenue (1)'!B13</f>
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K20" s="9" t="str">
         <f ca="1">'Baltų Avenue (1)'!S3</f>
@@ -4537,7 +4546,7 @@
       </c>
       <c r="J21" s="9">
         <f ca="1">'"Filleo Home", Palanga (3)'!B13</f>
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="K21" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!S3</f>
@@ -4549,7 +4558,7 @@
       </c>
       <c r="M21" s="5">
         <f>'"Filleo Home", Palanga (3)'!P3</f>
-        <v>3.98</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="AC21" s="5" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!AA2</f>
@@ -4594,23 +4603,23 @@
       </c>
       <c r="J22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!B13</f>
-        <v>215</v>
-      </c>
-      <c r="K22" s="9">
+        <v>208</v>
+      </c>
+      <c r="K22" s="9" t="str">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!S3</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="L22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!N3</f>
-        <v>7.61</v>
+        <v>18.2</v>
       </c>
       <c r="M22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!P3</f>
-        <v>3.2100000000000004</v>
+        <v>3.7900000000000005</v>
       </c>
       <c r="AC22" s="5" t="str">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
@@ -4651,11 +4660,11 @@
       </c>
       <c r="J23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!B13</f>
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!S3</f>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="L23" s="5">
         <f>'Liepų g. 3, Vyšniūnai (1)'!N3</f>
@@ -4708,7 +4717,7 @@
       </c>
       <c r="J24" s="9">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!B13</f>
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="K24" s="9" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!S3</f>
@@ -4765,11 +4774,11 @@
       </c>
       <c r="J25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!B13</f>
-        <v>258</v>
-      </c>
-      <c r="K25" s="9">
+        <v>251</v>
+      </c>
+      <c r="K25" s="9" t="str">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!S3</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="L25" s="5">
         <f>'Mėguvos g. 6 ir 8, Palanga (2)'!N3</f>
@@ -4777,11 +4786,11 @@
       </c>
       <c r="M25" s="5">
         <f>'Mėguvos g. 6 ir 8, Palanga (2)'!P3</f>
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" s="5" t="str">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
@@ -4822,7 +4831,7 @@
       </c>
       <c r="J26" s="9">
         <f ca="1">'"Filleo Home", Palanga (10)'!B13</f>
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="K26" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!S3</f>
@@ -4879,7 +4888,7 @@
       </c>
       <c r="J27" s="9">
         <f ca="1">'Baltų Avenue (11)'!B13</f>
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="K27" s="9" t="str">
         <f ca="1">'Baltų Avenue (11)'!S3</f>
@@ -4891,7 +4900,7 @@
       </c>
       <c r="M27" s="5">
         <f>'Baltų Avenue (11)'!P3</f>
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" s="5" t="str">
         <f ca="1">'Baltų Avenue (11)'!AA2</f>
@@ -4936,7 +4945,7 @@
       </c>
       <c r="J28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!B13</f>
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="K28" s="9" t="str">
         <f ca="1">'Plento g. 5A, Trakai (2)'!S3</f>
@@ -5056,21 +5065,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -5130,9 +5139,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -5195,7 +5204,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.98</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -5401,13 +5410,21 @@
       <c r="F8" s="5">
         <v>0.67</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8">
+        <v>46239</v>
+      </c>
+      <c r="K8" s="9">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="Y8" s="8">
         <f t="shared" si="1"/>
@@ -5444,11 +5461,11 @@
       </c>
       <c r="Y9" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Z9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
@@ -5556,7 +5573,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D13" s="8">
         <v>46371</v>
@@ -6201,7 +6218,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>3.98</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -6298,21 +6315,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -6372,9 +6389,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -6820,7 +6837,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="D13" s="8">
         <v>46345</v>
@@ -7667,21 +7684,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -7741,9 +7758,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -8968,21 +8985,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -9042,9 +9059,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -9119,7 +9136,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -9466,7 +9483,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D13" s="8">
         <v>46323</v>
@@ -10211,21 +10228,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -10285,9 +10302,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -10362,7 +10379,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -10741,7 +10758,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D13" s="8">
         <v>46284</v>
@@ -11483,21 +11500,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -11557,9 +11574,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -11622,7 +11639,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>5.36</v>
+        <v>5.91</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -11992,13 +12009,21 @@
       <c r="F12" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>46239</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="0"/>
+        <v>-3</v>
       </c>
       <c r="Y12" s="8">
         <f t="shared" si="1"/>
@@ -12015,7 +12040,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D13" s="8">
         <v>46273</v>
@@ -12036,11 +12061,11 @@
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46239</v>
       </c>
       <c r="Z13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -12732,7 +12757,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>5.36</v>
+        <v>5.91</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -12783,6 +12808,9 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12830,21 +12858,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -12904,9 +12932,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -12969,7 +12997,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>5.07</v>
+        <v>5.59</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -13339,13 +13367,21 @@
       <c r="F12" s="5">
         <v>0.52</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>46237</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Y12" s="8">
         <f t="shared" si="1"/>
@@ -13362,7 +13398,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D13" s="8">
         <v>46248</v>
@@ -13383,11 +13419,11 @@
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Z13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -14007,7 +14043,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>5.07</v>
+        <v>5.59</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -14107,21 +14143,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -14181,9 +14217,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -15304,21 +15340,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -15378,9 +15414,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -15455,7 +15491,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -15836,7 +15872,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-25</v>
+        <v>-32</v>
       </c>
       <c r="D13" s="8">
         <v>46207</v>
@@ -16578,21 +16614,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -16652,9 +16688,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -17947,7 +17983,7 @@
       </c>
       <c r="L1" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15313978791236879</v>
+        <v>0.15337591767311098</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -19752,14 +19788,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="28">
         <f>Apžvalga!U3</f>
-        <v>1111.8500000000001</v>
+        <v>1115.1500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -19821,21 +19857,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -19895,9 +19931,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -19972,7 +20008,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -20353,7 +20389,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D13" s="8">
         <v>46199</v>
@@ -21170,21 +21206,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -21244,9 +21280,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -22466,21 +22502,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -22540,9 +22576,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -23691,21 +23727,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -23765,9 +23801,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -25000,21 +25036,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -25074,9 +25110,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -26306,21 +26342,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -26380,9 +26416,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -26846,7 +26882,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D13" s="8">
         <v>46101</v>
@@ -27717,21 +27753,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -27791,9 +27827,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -27868,7 +27904,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -28209,7 +28245,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-204</v>
+        <v>-211</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -28947,21 +28983,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -29021,9 +29057,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -29098,7 +29134,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -29487,7 +29523,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="D13" s="8">
         <v>46086</v>
@@ -30303,21 +30339,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -30377,9 +30413,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -31623,21 +31659,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -31689,9 +31725,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -32075,7 +32111,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D13" s="8">
         <v>46561</v>
@@ -32668,21 +32704,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -32742,9 +32778,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -32807,7 +32843,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -32849,13 +32885,21 @@
       <c r="F4" s="5">
         <v>0.45</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>46238</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>-4</v>
       </c>
       <c r="Y4" s="8">
         <f t="shared" ref="Y4:Y41" si="1">J3</f>
@@ -32892,11 +32936,11 @@
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46238</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -33136,7 +33180,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="D13" s="8">
         <v>46515</v>
@@ -33841,7 +33885,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -33938,21 +33982,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -34012,9 +34056,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -34388,7 +34432,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -35077,9 +35121,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCADA21-0698-4157-B17D-6AAD26A4F890}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -35127,21 +35168,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -35201,9 +35242,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -35217,7 +35258,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -35266,7 +35307,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -35276,9 +35317,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -35308,13 +35349,21 @@
       <c r="F4" s="5">
         <v>0.51</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="J4" s="8">
+        <v>46237</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="Y4" s="8">
         <f t="shared" ref="Y4:Y41" si="1">J3</f>
@@ -35351,11 +35400,11 @@
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -35595,7 +35644,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D13" s="8">
         <v>46490</v>
@@ -36240,11 +36289,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -36337,21 +36386,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -36411,9 +36460,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -36821,7 +36870,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D13" s="8">
         <v>46455</v>
@@ -37638,21 +37687,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -37712,9 +37761,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -37789,7 +37838,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -38114,7 +38163,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D13" s="8">
         <v>46429</v>
@@ -38859,21 +38908,21 @@
       <c r="K1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="36"/>
-      <c r="O1" s="34" t="s">
+      <c r="M1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="37"/>
+      <c r="O1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="42" t="s">
         <v>83</v>
       </c>
       <c r="T1" s="20"/>
@@ -38933,9 +38982,9 @@
       <c r="P2" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
@@ -38949,7 +38998,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -38990,7 +39039,7 @@
       </c>
       <c r="N3" s="5">
         <f>G42</f>
-        <v>7.61</v>
+        <v>18.2</v>
       </c>
       <c r="O3" s="5">
         <f>F42</f>
@@ -38998,7 +39047,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.2100000000000004</v>
+        <v>3.7900000000000005</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -39008,9 +39057,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -39160,16 +39209,24 @@
       <c r="E7" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="34">
         <v>0.64</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G7" s="5">
+        <v>10.59</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="J7" s="8">
+        <v>46237</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>27</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="1"/>
@@ -39193,7 +39250,7 @@
       <c r="E8" s="5">
         <v>0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="34">
         <v>0.66</v>
       </c>
       <c r="G8" s="5"/>
@@ -39206,11 +39263,11 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
@@ -39226,7 +39283,7 @@
       <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="34">
         <v>0.66</v>
       </c>
       <c r="G9" s="5"/>
@@ -39259,7 +39316,7 @@
       <c r="E10" s="5">
         <v>0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="34">
         <v>0.64</v>
       </c>
       <c r="G10" s="5"/>
@@ -39292,7 +39349,7 @@
       <c r="E11" s="5">
         <v>0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="34">
         <v>0.66</v>
       </c>
       <c r="G11" s="5"/>
@@ -39325,7 +39382,7 @@
       <c r="E12" s="5">
         <v>0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="34">
         <v>0.64</v>
       </c>
       <c r="G12" s="5"/>
@@ -39351,7 +39408,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D13" s="8">
         <v>46394</v>
@@ -39359,7 +39416,7 @@
       <c r="E13" s="5">
         <v>0</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="34">
         <v>0.66</v>
       </c>
       <c r="G13" s="5"/>
@@ -39390,7 +39447,7 @@
       <c r="E14" s="5">
         <v>0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="34">
         <v>0.66</v>
       </c>
       <c r="G14" s="5"/>
@@ -39424,7 +39481,7 @@
       <c r="E15" s="5">
         <v>60</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="34">
         <v>0.5</v>
       </c>
       <c r="G15" s="5"/>
@@ -40004,15 +40061,15 @@
       </c>
       <c r="G42" s="5">
         <f t="shared" si="4"/>
-        <v>7.61</v>
+        <v>18.2</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>3.2100000000000004</v>
+        <v>3.7600000000000007</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>

--- a/excel/Nordstreet.xlsx
+++ b/excel/Nordstreet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Nordstreet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C49BCC-641F-40CF-8CCC-CC4EBED43235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C2263E-0998-47DB-BB8D-5B72A05A20BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apžvalga" sheetId="1" r:id="rId1"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>91.860000000000127</v>
+        <v>93.220000000000027</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -3516,23 +3516,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>116.21</v>
+        <v>117.57</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1115.1500000000001</v>
+        <v>1116.51</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>165.15000000000009</v>
+        <v>166.51</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>0.17384210526315799</v>
+        <v>0.1752736842105263</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15337591767311098</v>
+        <v>0.15263281464576722</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mesiheina tee 5 ir 8 (1)'!AA2</f>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="J4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!B13</f>
-        <v>-26</v>
+        <v>-31</v>
       </c>
       <c r="K4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!S3</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L4" s="5">
         <f>'Bistryčios g. 27 (3)'!N3</f>
@@ -3634,11 +3634,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!B13</f>
-        <v>-211</v>
+        <v>-216</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!S3</f>
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="L5" s="5">
         <f>'2 MW saulės elektrinių par. (9)'!N3</f>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!B13</f>
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!S3</f>
@@ -3976,11 +3976,11 @@
       </c>
       <c r="J11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!B13</f>
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="K11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!S3</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!N3</f>
@@ -4090,11 +4090,11 @@
       </c>
       <c r="J13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!B13</f>
-        <v>-32</v>
+        <v>-37</v>
       </c>
       <c r="K13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!S3</f>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L13" s="5">
         <f>'Vilniaus g. 38 38A 38B (1)'!N3</f>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="J15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!B13</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K15" s="9" t="str">
         <f ca="1">'Viensėdžio g. 36A (3)'!S3</f>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="J16" s="9">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!B13</f>
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="K16" s="9" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!S3</f>
@@ -4318,11 +4318,11 @@
       </c>
       <c r="J17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!B13</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!S3</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L17" s="5">
         <f>'Mozūriškių g. 17 - 3, Vilnius'!N3</f>
@@ -4375,11 +4375,11 @@
       </c>
       <c r="J18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!B13</f>
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!S3</f>
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L18" s="5">
         <f>'Parko g. 21 Pergalės g. 36A (1)'!N3</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J20" s="9">
         <f ca="1">'Baltų Avenue (1)'!B13</f>
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="K20" s="9" t="str">
         <f ca="1">'Baltų Avenue (1)'!S3</f>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="J21" s="9">
         <f ca="1">'"Filleo Home", Palanga (3)'!B13</f>
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K21" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!S3</f>
@@ -4603,11 +4603,11 @@
       </c>
       <c r="J22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!B13</f>
-        <v>208</v>
-      </c>
-      <c r="K22" s="9" t="str">
+        <v>203</v>
+      </c>
+      <c r="K22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!S3</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="L22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!N3</f>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AC22" s="5" t="str">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
@@ -4660,11 +4660,11 @@
       </c>
       <c r="J23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!B13</f>
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!S3</f>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L23" s="5">
         <f>'Liepų g. 3, Vyšniūnai (1)'!N3</f>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="J24" s="9">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!B13</f>
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="K24" s="9" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!S3</f>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="M24" s="5">
         <f>'Basliupio g. 14, Panevėžys (3)'!P3</f>
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="AC24" s="5" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!AA2</f>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="J25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!B13</f>
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K25" s="9" t="str">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!S3</f>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="J26" s="9">
         <f ca="1">'"Filleo Home", Palanga (10)'!B13</f>
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K26" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!S3</f>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M26" s="5">
         <f>'"Filleo Home", Palanga (10)'!P3</f>
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" s="5" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!AA2</f>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J27" s="9">
         <f ca="1">'Baltų Avenue (11)'!B13</f>
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="K27" s="9" t="str">
         <f ca="1">'Baltų Avenue (11)'!S3</f>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="J28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!B13</f>
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="K28" s="9" t="str">
         <f ca="1">'Plento g. 5A, Trakai (2)'!S3</f>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D13" s="8">
         <v>46371</v>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D13" s="8">
         <v>46345</v>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D13" s="8">
         <v>46323</v>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D13" s="8">
         <v>46284</v>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D13" s="8">
         <v>46273</v>
@@ -12808,9 +12808,6 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13398,7 +13395,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" s="8">
         <v>46248</v>
@@ -15491,7 +15488,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -15872,7 +15869,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-32</v>
+        <v>-37</v>
       </c>
       <c r="D13" s="8">
         <v>46207</v>
@@ -17983,7 +17980,7 @@
       </c>
       <c r="L1" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15337591767311098</v>
+        <v>0.15263281464576722</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -19788,14 +19785,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f ca="1">TODAY()</f>
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="28">
         <f>Apžvalga!U3</f>
-        <v>1115.1500000000001</v>
+        <v>1116.51</v>
       </c>
     </row>
   </sheetData>
@@ -20008,7 +20005,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -20389,7 +20386,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D13" s="8">
         <v>46199</v>
@@ -26882,7 +26879,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D13" s="8">
         <v>46101</v>
@@ -27904,7 +27901,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -28245,7 +28242,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-211</v>
+        <v>-216</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -29134,7 +29131,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -29523,7 +29520,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-26</v>
+        <v>-31</v>
       </c>
       <c r="D13" s="8">
         <v>46086</v>
@@ -32111,7 +32108,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D13" s="8">
         <v>46561</v>
@@ -33180,7 +33177,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D13" s="8">
         <v>46515</v>
@@ -34121,7 +34118,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -34163,13 +34160,21 @@
       <c r="F4" s="5">
         <v>0.76</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>46244</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="Y4" s="8">
         <f t="shared" ref="Y4:Y41" si="1">J3</f>
@@ -34206,11 +34211,11 @@
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46244</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -34432,7 +34437,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -35071,7 +35076,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -35644,7 +35649,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D13" s="8">
         <v>46490</v>
@@ -36525,7 +36530,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -36649,13 +36654,21 @@
       <c r="F6" s="5">
         <v>0.6</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>46244</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="1"/>
@@ -36692,11 +36705,11 @@
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46244</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -36870,7 +36883,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D13" s="8">
         <v>46455</v>
@@ -37587,7 +37600,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -37838,7 +37851,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -38163,7 +38176,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D13" s="8">
         <v>46429</v>
@@ -38998,7 +39011,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -39057,9 +39070,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -39408,7 +39421,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D13" s="8">
         <v>46394</v>

--- a/excel/Nordstreet.xlsx
+++ b/excel/Nordstreet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C2263E-0998-47DB-BB8D-5B72A05A20BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3502F2B2-34BD-4A3C-BBEB-D00378A0E280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="O3" s="5">
         <f>Pinigai!I2</f>
-        <v>950</v>
+        <v>854.83</v>
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
-        <v>1023.29</v>
+        <v>1023.79</v>
       </c>
       <c r="Q3" s="5">
         <f>Pinigai!H2</f>
@@ -3508,31 +3508,31 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>93.220000000000027</v>
+        <v>1.3400000000001455</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
-        <v>432.71</v>
+        <v>432.21</v>
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>117.57</v>
+        <v>121.36</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1116.51</v>
+        <v>1025.1300000000001</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>166.51</v>
+        <v>170.30000000000007</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>0.1752736842105263</v>
+        <v>0.19922089772235421</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15263281464576722</v>
+        <v>0.14719318747520452</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mesiheina tee 5 ir 8 (1)'!AA2</f>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="J4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!B13</f>
-        <v>-31</v>
+        <v>-53</v>
       </c>
       <c r="K4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!S3</f>
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L4" s="5">
         <f>'Bistryčios g. 27 (3)'!N3</f>
@@ -3634,11 +3634,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!B13</f>
-        <v>-216</v>
+        <v>-238</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!S3</f>
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="L5" s="5">
         <f>'2 MW saulės elektrinių par. (9)'!N3</f>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!B13</f>
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!S3</f>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="M6" s="5">
         <f>'Kvartalas "Asiūklės parkas” (2)'!P3</f>
-        <v>7.2500000000000009</v>
+        <v>7.7100000000000009</v>
       </c>
       <c r="AC6" s="5" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!AA2</f>
@@ -3976,11 +3976,11 @@
       </c>
       <c r="J11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!B13</f>
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="K11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!S3</f>
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="L11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!N3</f>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="M11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!P3</f>
-        <v>7.7200000000000006</v>
+        <v>8.5100000000000016</v>
       </c>
       <c r="AC11" s="5" t="str">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!AA2</f>
@@ -4090,11 +4090,11 @@
       </c>
       <c r="J13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!B13</f>
-        <v>-37</v>
+        <v>-59</v>
       </c>
       <c r="K13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!S3</f>
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L13" s="5">
         <f>'Vilniaus g. 38 38A 38B (1)'!N3</f>
@@ -4204,11 +4204,11 @@
       </c>
       <c r="J15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!B13</f>
-        <v>4</v>
-      </c>
-      <c r="K15" s="9" t="str">
+        <v>-18</v>
+      </c>
+      <c r="K15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!S3</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="L15" s="5">
         <f>'Viensėdžio g. 36A (3)'!N3</f>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="AC15" s="5" t="str">
         <f ca="1">'Viensėdžio g. 36A (3)'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="J16" s="9">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!B13</f>
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="K16" s="9" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!S3</f>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="M16" s="5">
         <f>'Šaltinio g. 7, Panevėžys (1)'!P3</f>
-        <v>5.91</v>
+        <v>6.46</v>
       </c>
       <c r="AC16" s="5" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!AA2</f>
@@ -4318,11 +4318,11 @@
       </c>
       <c r="J17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!B13</f>
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!S3</f>
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L17" s="5">
         <f>'Mozūriškių g. 17 - 3, Vilnius'!N3</f>
@@ -4375,11 +4375,11 @@
       </c>
       <c r="J18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!B13</f>
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="K18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!S3</f>
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="L18" s="5">
         <f>'Parko g. 21 Pergalės g. 36A (1)'!N3</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J20" s="9">
         <f ca="1">'Baltų Avenue (1)'!B13</f>
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="K20" s="9" t="str">
         <f ca="1">'Baltų Avenue (1)'!S3</f>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="M20" s="5">
         <f>'Baltų Avenue (1)'!P3</f>
-        <v>5.5500000000000007</v>
+        <v>6.2600000000000007</v>
       </c>
       <c r="AC20" s="5" t="str">
         <f ca="1">'Baltų Avenue (1)'!AA2</f>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="J21" s="9">
         <f ca="1">'"Filleo Home", Palanga (3)'!B13</f>
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="K21" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!S3</f>
@@ -4603,19 +4603,19 @@
       </c>
       <c r="J22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!B13</f>
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="K22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!S3</f>
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="L22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!N3</f>
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="M22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!P3</f>
-        <v>3.7900000000000005</v>
+        <v>4.2900000000000009</v>
       </c>
       <c r="AC22" s="5" t="str">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!AA2</f>
@@ -4660,11 +4660,11 @@
       </c>
       <c r="J23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!B13</f>
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="K23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!S3</f>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L23" s="5">
         <f>'Liepų g. 3, Vyšniūnai (1)'!N3</f>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="M23" s="5">
         <f>'Liepų g. 3, Vyšniūnai (1)'!P3</f>
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="AC23" s="5" t="str">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!AA2</f>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="J24" s="9">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!B13</f>
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="K24" s="9" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!S3</f>
@@ -4774,11 +4774,11 @@
       </c>
       <c r="J25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!B13</f>
-        <v>246</v>
-      </c>
-      <c r="K25" s="9" t="str">
+        <v>224</v>
+      </c>
+      <c r="K25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!S3</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="L25" s="5">
         <f>'Mėguvos g. 6 ir 8, Palanga (2)'!N3</f>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AC25" s="5" t="str">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="J26" s="9">
         <f ca="1">'"Filleo Home", Palanga (10)'!B13</f>
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="K26" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!S3</f>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J27" s="9">
         <f ca="1">'Baltų Avenue (11)'!B13</f>
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="K27" s="9" t="str">
         <f ca="1">'Baltų Avenue (11)'!S3</f>
@@ -4945,11 +4945,11 @@
       </c>
       <c r="J28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!B13</f>
-        <v>317</v>
-      </c>
-      <c r="K28" s="9" t="str">
+        <v>295</v>
+      </c>
+      <c r="K28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!S3</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="L28" s="5">
         <f>'Plento g. 5A, Trakai (2)'!N3</f>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="AC28" s="5" t="str">
         <f ca="1">'Plento g. 5A, Trakai (2)'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
   </sheetData>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D13" s="8">
         <v>46371</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>5.5500000000000007</v>
+        <v>6.2600000000000007</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -6746,13 +6746,21 @@
       <c r="F10" s="5">
         <v>0.71</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>46251</v>
+      </c>
+      <c r="K10" s="9">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y10" s="8">
         <f t="shared" si="1"/>
@@ -6790,11 +6798,11 @@
       </c>
       <c r="Y11" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46251</v>
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -6837,7 +6845,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="D13" s="8">
         <v>46345</v>
@@ -7584,7 +7592,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>5.5500000000000007</v>
+        <v>6.2600000000000007</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -9136,7 +9144,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -9483,7 +9491,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D13" s="8">
         <v>46323</v>
@@ -10379,7 +10387,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -10758,7 +10766,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D13" s="8">
         <v>46284</v>
@@ -11639,7 +11647,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>5.91</v>
+        <v>6.46</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -12040,7 +12048,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="D13" s="8">
         <v>46273</v>
@@ -12051,13 +12059,21 @@
       <c r="F13" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>46266</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="0"/>
+        <v>-7</v>
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="1"/>
@@ -12092,11 +12108,11 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46266</v>
       </c>
       <c r="Z14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -12757,7 +12773,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>5.91</v>
+        <v>6.46</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -12945,7 +12961,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -13004,9 +13020,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -13395,7 +13411,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="D13" s="8">
         <v>46248</v>
@@ -15488,7 +15504,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -15869,7 +15885,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-37</v>
+        <v>-59</v>
       </c>
       <c r="D13" s="8">
         <v>46207</v>
@@ -17980,7 +17996,7 @@
       </c>
       <c r="L1" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15263281464576722</v>
+        <v>0.14719318747520452</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -18002,7 +18018,7 @@
       </c>
       <c r="G2" s="5">
         <f>SUM(C2:C44)</f>
-        <v>0</v>
+        <v>95.17</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(D2:D44)</f>
@@ -18010,7 +18026,7 @@
       </c>
       <c r="I2" s="5">
         <f>F2-G2</f>
-        <v>950</v>
+        <v>854.83</v>
       </c>
       <c r="K2" s="5">
         <f>B2*-1</f>
@@ -18649,18 +18665,39 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="K38" s="2"/>
+      <c r="A38" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B38" s="5">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5">
+        <v>94.17</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5">
+        <f>C38</f>
+        <v>94.17</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="K39" s="2"/>
+      <c r="A39" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B39" s="5">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
@@ -19785,14 +19822,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="28">
         <f>Apžvalga!U3</f>
-        <v>1116.51</v>
+        <v>1025.1300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -19993,7 +20030,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>7.7200000000000006</v>
+        <v>8.5100000000000016</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -20005,7 +20042,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -20363,13 +20400,21 @@
       <c r="F12" s="5">
         <v>0.67</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="J12" s="8">
+        <v>46255</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="0"/>
+        <v>87</v>
       </c>
       <c r="Y12" s="8">
         <f t="shared" si="1"/>
@@ -20386,7 +20431,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="D13" s="8">
         <v>46199</v>
@@ -20407,11 +20452,11 @@
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46255</v>
       </c>
       <c r="Z13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -21103,11 +21148,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>6.8400000000000007</v>
+        <v>7.5100000000000007</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -26478,7 +26523,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>7.2500000000000009</v>
+        <v>7.7100000000000009</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -26879,7 +26924,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D13" s="8">
         <v>46101</v>
@@ -27111,13 +27156,21 @@
       <c r="F19" s="3">
         <v>0.46</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>46252</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y19" s="8">
         <f t="shared" si="1"/>
@@ -27148,11 +27201,11 @@
       </c>
       <c r="Y20" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46252</v>
       </c>
       <c r="Z20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
@@ -27650,7 +27703,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>7.2500000000000009</v>
+        <v>7.7100000000000009</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -27901,7 +27954,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -28242,7 +28295,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-216</v>
+        <v>-238</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -29131,7 +29184,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -29520,7 +29573,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-31</v>
+        <v>-53</v>
       </c>
       <c r="D13" s="8">
         <v>46086</v>
@@ -31738,7 +31791,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -31789,9 +31842,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -32108,7 +32161,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="D13" s="8">
         <v>46561</v>
@@ -33177,7 +33230,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="D13" s="8">
         <v>46515</v>
@@ -34437,7 +34490,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -35263,7 +35316,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -35322,9 +35375,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -35649,7 +35702,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D13" s="8">
         <v>46490</v>
@@ -36883,7 +36936,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="D13" s="8">
         <v>46455</v>
@@ -37839,7 +37892,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -37851,7 +37904,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -37922,13 +37975,21 @@
       <c r="F5" s="5">
         <v>0.69</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J5" s="8">
+        <v>46252</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>67</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
@@ -37965,11 +38026,11 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46252</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.77999999999999992</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -38176,7 +38237,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D13" s="8">
         <v>46429</v>
@@ -38821,11 +38882,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>1.98</v>
+        <v>2.67</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0.16000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -39052,7 +39113,7 @@
       </c>
       <c r="N3" s="5">
         <f>G42</f>
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="O3" s="5">
         <f>F42</f>
@@ -39060,7 +39121,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.7900000000000005</v>
+        <v>4.2900000000000009</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -39072,7 +39133,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -39226,10 +39287,10 @@
         <v>0.64</v>
       </c>
       <c r="G7" s="5">
-        <v>10.59</v>
+        <v>10.09</v>
       </c>
       <c r="H7" s="5">
-        <v>0.55000000000000004</v>
+        <v>1.05</v>
       </c>
       <c r="I7" s="5">
         <v>0.03</v>
@@ -39421,7 +39482,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="D13" s="8">
         <v>46394</v>
@@ -40074,11 +40135,11 @@
       </c>
       <c r="G42" s="5">
         <f t="shared" si="4"/>
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>3.7600000000000007</v>
+        <v>4.2600000000000007</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
